--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/53.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/53.xlsx
@@ -426,13 +426,13 @@
         <v>-10.75686131360146</v>
       </c>
       <c r="E2">
-        <v>-28.74223113186537</v>
+        <v>-34.44197229924963</v>
       </c>
       <c r="F2">
-        <v>-5.79248346643347</v>
+        <v>-6.388642918880219</v>
       </c>
       <c r="G2">
-        <v>-16.9018920850512</v>
+        <v>-18.61589558782623</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-10.13467581830358</v>
       </c>
       <c r="E3">
-        <v>-27.50010693935345</v>
+        <v>-34.92948516854538</v>
       </c>
       <c r="F3">
-        <v>-5.83461588927466</v>
+        <v>-6.280695877519207</v>
       </c>
       <c r="G3">
-        <v>-15.44920152860023</v>
+        <v>-18.76330590432613</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-9.477497837348565</v>
       </c>
       <c r="E4">
-        <v>-28.46036532420594</v>
+        <v>-36.48703342535056</v>
       </c>
       <c r="F4">
-        <v>-6.086128941949659</v>
+        <v>-5.288010203230781</v>
       </c>
       <c r="G4">
-        <v>-15.53986578401148</v>
+        <v>-19.26524916371766</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-8.833496586224614</v>
       </c>
       <c r="E5">
-        <v>-28.75731095031091</v>
+        <v>-34.48528036042198</v>
       </c>
       <c r="F5">
-        <v>-5.979831180087621</v>
+        <v>-6.453114753840104</v>
       </c>
       <c r="G5">
-        <v>-15.84255061793981</v>
+        <v>-18.41033884947458</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-8.208251185111811</v>
       </c>
       <c r="E6">
-        <v>-28.53058837064289</v>
+        <v>-36.54794366499073</v>
       </c>
       <c r="F6">
-        <v>-6.097274625354326</v>
+        <v>-5.865455179313482</v>
       </c>
       <c r="G6">
-        <v>-15.30320812559114</v>
+        <v>-18.63697714182031</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-7.624273950441214</v>
       </c>
       <c r="E7">
-        <v>-29.36426685003298</v>
+        <v>-36.06140215336963</v>
       </c>
       <c r="F7">
-        <v>-6.067437659872891</v>
+        <v>-6.102562922853799</v>
       </c>
       <c r="G7">
-        <v>-14.93153979898824</v>
+        <v>-19.28570833515036</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-7.088390146435819</v>
       </c>
       <c r="E8">
-        <v>-29.67446279108439</v>
+        <v>-36.80643122558556</v>
       </c>
       <c r="F8">
-        <v>-6.037324019678921</v>
+        <v>-6.098677051367266</v>
       </c>
       <c r="G8">
-        <v>-14.96634190896983</v>
+        <v>-18.46823366986535</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-6.608988291180435</v>
       </c>
       <c r="E9">
-        <v>-30.11202206360153</v>
+        <v>-36.83552440684784</v>
       </c>
       <c r="F9">
-        <v>-5.762891697703264</v>
+        <v>-5.466501840981601</v>
       </c>
       <c r="G9">
-        <v>-15.04216002291022</v>
+        <v>-18.4516859079873</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-6.18522829882067</v>
       </c>
       <c r="E10">
-        <v>-29.75866976525702</v>
+        <v>-35.27580701099298</v>
       </c>
       <c r="F10">
-        <v>-5.495948645416318</v>
+        <v>-5.857520247962065</v>
       </c>
       <c r="G10">
-        <v>-14.86681863369549</v>
+        <v>-18.88531274963043</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-5.814567952279931</v>
       </c>
       <c r="E11">
-        <v>-30.34195306710399</v>
+        <v>-38.69649400758896</v>
       </c>
       <c r="F11">
-        <v>-5.613812072956242</v>
+        <v>-6.062730047922781</v>
       </c>
       <c r="G11">
-        <v>-14.36575266887187</v>
+        <v>-19.0298793075121</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-5.490185606550398</v>
       </c>
       <c r="E12">
-        <v>-30.80690281465652</v>
+        <v>-38.23080611877317</v>
       </c>
       <c r="F12">
-        <v>-5.384405661159753</v>
+        <v>-5.3790047056935</v>
       </c>
       <c r="G12">
-        <v>-15.72055370427213</v>
+        <v>-18.83537317017053</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-5.201999263789347</v>
       </c>
       <c r="E13">
-        <v>-30.96219324532755</v>
+        <v>-38.66354256647215</v>
       </c>
       <c r="F13">
-        <v>-5.675782238359673</v>
+        <v>-5.654685377345175</v>
       </c>
       <c r="G13">
-        <v>-15.49159140895783</v>
+        <v>-18.55851059144851</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-4.948277432178378</v>
       </c>
       <c r="E14">
-        <v>-30.21216700204415</v>
+        <v>-36.42871347284278</v>
       </c>
       <c r="F14">
-        <v>-5.353444601112718</v>
+        <v>-5.631053712078112</v>
       </c>
       <c r="G14">
-        <v>-14.93103825133904</v>
+        <v>-17.89554736284514</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-4.723839336839531</v>
       </c>
       <c r="E15">
-        <v>-31.52209150739891</v>
+        <v>-37.97923353798806</v>
       </c>
       <c r="F15">
-        <v>-5.724785140439681</v>
+        <v>-5.474947875020544</v>
       </c>
       <c r="G15">
-        <v>-14.71247603483636</v>
+        <v>-17.63187565282434</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-4.52700049767982</v>
       </c>
       <c r="E16">
-        <v>-31.50848570724287</v>
+        <v>-38.52507994521362</v>
       </c>
       <c r="F16">
-        <v>-4.848052678460324</v>
+        <v>-4.529793093937351</v>
       </c>
       <c r="G16">
-        <v>-14.92073914416637</v>
+        <v>-17.9157632091807</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-4.35598548607896</v>
       </c>
       <c r="E17">
-        <v>-32.11752470500846</v>
+        <v>-39.09422535120864</v>
       </c>
       <c r="F17">
-        <v>-5.229251618248003</v>
+        <v>-5.248612221186232</v>
       </c>
       <c r="G17">
-        <v>-14.13674899173832</v>
+        <v>-19.33294816472299</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-4.209522601747008</v>
       </c>
       <c r="E18">
-        <v>-32.94785211363288</v>
+        <v>-38.31570368523197</v>
       </c>
       <c r="F18">
-        <v>-4.929952535207708</v>
+        <v>-5.104752967811654</v>
       </c>
       <c r="G18">
-        <v>-13.96378291894802</v>
+        <v>-18.09330611117904</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-4.085798620320435</v>
       </c>
       <c r="E19">
-        <v>-32.7822073271433</v>
+        <v>-39.36756177807462</v>
       </c>
       <c r="F19">
-        <v>-4.669800438888912</v>
+        <v>-4.245720232127914</v>
       </c>
       <c r="G19">
-        <v>-14.26518491647989</v>
+        <v>-17.28196919732385</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-3.981369967567232</v>
       </c>
       <c r="E20">
-        <v>-33.70670435275722</v>
+        <v>-38.51956879234628</v>
       </c>
       <c r="F20">
-        <v>-4.38377925694809</v>
+        <v>-4.399292921667719</v>
       </c>
       <c r="G20">
-        <v>-14.44994149720831</v>
+        <v>-18.23881451926663</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-3.896584281134721</v>
       </c>
       <c r="E21">
-        <v>-34.18719582310408</v>
+        <v>-39.83111222715878</v>
       </c>
       <c r="F21">
-        <v>-4.307859384481516</v>
+        <v>-4.596477498230113</v>
       </c>
       <c r="G21">
-        <v>-14.48064680708505</v>
+        <v>-17.8977952232663</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-3.829350321209826</v>
       </c>
       <c r="E22">
-        <v>-33.6525551248105</v>
+        <v>-39.35853200090332</v>
       </c>
       <c r="F22">
-        <v>-4.034127032961225</v>
+        <v>-4.38711095064215</v>
       </c>
       <c r="G22">
-        <v>-14.0525320237648</v>
+        <v>-18.21337297679733</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-3.780495546671106</v>
       </c>
       <c r="E23">
-        <v>-33.77903993231875</v>
+        <v>-38.32519310251505</v>
       </c>
       <c r="F23">
-        <v>-4.025467280132358</v>
+        <v>-4.533647487462577</v>
       </c>
       <c r="G23">
-        <v>-14.22482936635617</v>
+        <v>-18.79593298588842</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-3.750536696371945</v>
       </c>
       <c r="E24">
-        <v>-33.84970450497144</v>
+        <v>-38.64042017818898</v>
       </c>
       <c r="F24">
-        <v>-4.071748995294169</v>
+        <v>-3.804475424413506</v>
       </c>
       <c r="G24">
-        <v>-14.62960976944286</v>
+        <v>-18.80322280716589</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-3.740349901547761</v>
       </c>
       <c r="E25">
-        <v>-34.44275572525295</v>
+        <v>-39.97048280745585</v>
       </c>
       <c r="F25">
-        <v>-4.144819283895114</v>
+        <v>-4.370314973182987</v>
       </c>
       <c r="G25">
-        <v>-15.19121568054313</v>
+        <v>-18.72660850702331</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-3.750559033814767</v>
       </c>
       <c r="E26">
-        <v>-34.18170278413278</v>
+        <v>-37.87466428043994</v>
       </c>
       <c r="F26">
-        <v>-4.029568527143619</v>
+        <v>-4.876026645652863</v>
       </c>
       <c r="G26">
-        <v>-15.25863162990485</v>
+        <v>-18.35735522339131</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-3.78037525342097</v>
       </c>
       <c r="E27">
-        <v>-35.21474280323655</v>
+        <v>-38.50348365267104</v>
       </c>
       <c r="F27">
-        <v>-3.961151178244199</v>
+        <v>-4.483254584880672</v>
       </c>
       <c r="G27">
-        <v>-14.72075901977562</v>
+        <v>-18.55601940593021</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-3.829979096755992</v>
       </c>
       <c r="E28">
-        <v>-34.43478561099946</v>
+        <v>-36.15879604385259</v>
       </c>
       <c r="F28">
-        <v>-4.307006994424035</v>
+        <v>-4.219344185655374</v>
       </c>
       <c r="G28">
-        <v>-14.84369447310368</v>
+        <v>-18.84056079503057</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-3.896701694869882</v>
       </c>
       <c r="E29">
-        <v>-33.97436433745459</v>
+        <v>-39.30717457718234</v>
       </c>
       <c r="F29">
-        <v>-3.99185378766156</v>
+        <v>-3.889053392974141</v>
       </c>
       <c r="G29">
-        <v>-15.08571024947933</v>
+        <v>-18.50336848967364</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-3.979749860296959</v>
       </c>
       <c r="E30">
-        <v>-32.6159489324257</v>
+        <v>-39.5695203976317</v>
       </c>
       <c r="F30">
-        <v>-4.248176341477214</v>
+        <v>-4.444865554332734</v>
       </c>
       <c r="G30">
-        <v>-14.32893609192963</v>
+        <v>-18.45183984835488</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-4.076723066256396</v>
       </c>
       <c r="E31">
-        <v>-33.27530154065351</v>
+        <v>-38.57086961014218</v>
       </c>
       <c r="F31">
-        <v>-3.96263395589521</v>
+        <v>-4.505832566811375</v>
       </c>
       <c r="G31">
-        <v>-14.52259638488592</v>
+        <v>-19.71956691498123</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-4.184452327250808</v>
       </c>
       <c r="E32">
-        <v>-33.18692837039382</v>
+        <v>-38.37177525039495</v>
       </c>
       <c r="F32">
-        <v>-4.366733112533282</v>
+        <v>-4.64058889079659</v>
       </c>
       <c r="G32">
-        <v>-14.75996250005166</v>
+        <v>-20.27108559382335</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-4.299167563219469</v>
       </c>
       <c r="E33">
-        <v>-32.55978679778256</v>
+        <v>-37.6536022932815</v>
       </c>
       <c r="F33">
-        <v>-3.842665646784772</v>
+        <v>-4.900059240742882</v>
       </c>
       <c r="G33">
-        <v>-15.14293137385286</v>
+        <v>-19.20200946755373</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-4.415600114977247</v>
       </c>
       <c r="E34">
-        <v>-32.48085096735487</v>
+        <v>-37.46515890440032</v>
       </c>
       <c r="F34">
-        <v>-4.390449271275432</v>
+        <v>-4.713030448538809</v>
       </c>
       <c r="G34">
-        <v>-14.33513343317915</v>
+        <v>-19.21399529767866</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-4.52816134099972</v>
       </c>
       <c r="E35">
-        <v>-32.25617978641232</v>
+        <v>-37.23398030630874</v>
       </c>
       <c r="F35">
-        <v>-4.534723536718813</v>
+        <v>-4.775159660483578</v>
       </c>
       <c r="G35">
-        <v>-14.78115826786685</v>
+        <v>-19.56082294582764</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-4.630658663166585</v>
       </c>
       <c r="E36">
-        <v>-31.50477688703059</v>
+        <v>-38.517039639613</v>
       </c>
       <c r="F36">
-        <v>-4.076080528443408</v>
+        <v>-4.100876878278808</v>
       </c>
       <c r="G36">
-        <v>-14.80670905833894</v>
+        <v>-19.57934544811986</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-4.717512179011332</v>
       </c>
       <c r="E37">
-        <v>-31.22440094731968</v>
+        <v>-37.15321044390794</v>
       </c>
       <c r="F37">
-        <v>-4.536412577853121</v>
+        <v>-5.150421691095393</v>
       </c>
       <c r="G37">
-        <v>-15.09244720965175</v>
+        <v>-18.9740568886289</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-4.783723259047162</v>
       </c>
       <c r="E38">
-        <v>-32.31025429453791</v>
+        <v>-36.46003239907983</v>
       </c>
       <c r="F38">
-        <v>-4.231538582191986</v>
+        <v>-4.827789155053042</v>
       </c>
       <c r="G38">
-        <v>-13.85012195894823</v>
+        <v>-19.92722419447756</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-4.824449393544968</v>
       </c>
       <c r="E39">
-        <v>-31.67211985127303</v>
+        <v>-35.72905065323569</v>
       </c>
       <c r="F39">
-        <v>-4.354595044980061</v>
+        <v>-4.157765838033468</v>
       </c>
       <c r="G39">
-        <v>-14.99660029519877</v>
+        <v>-19.4562626755153</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-4.83621191697339</v>
       </c>
       <c r="E40">
-        <v>-32.6621212534079</v>
+        <v>-35.9208722837266</v>
       </c>
       <c r="F40">
-        <v>-4.489548520407142</v>
+        <v>-4.123272619380896</v>
       </c>
       <c r="G40">
-        <v>-14.54114537154246</v>
+        <v>-19.15424822705867</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-4.816761748462171</v>
       </c>
       <c r="E41">
-        <v>-30.4367181784255</v>
+        <v>-35.24210384319089</v>
       </c>
       <c r="F41">
-        <v>-4.480474583876877</v>
+        <v>-5.120030547821485</v>
       </c>
       <c r="G41">
-        <v>-13.84324264531762</v>
+        <v>-19.71252207407366</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-4.765268481072415</v>
       </c>
       <c r="E42">
-        <v>-30.25434294471459</v>
+        <v>-37.88353103254696</v>
       </c>
       <c r="F42">
-        <v>-4.123067184265002</v>
+        <v>-4.863571313384369</v>
       </c>
       <c r="G42">
-        <v>-13.28436296846894</v>
+        <v>-18.59972853868521</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-4.684450165348971</v>
       </c>
       <c r="E43">
-        <v>-29.50392045995552</v>
+        <v>-37.38855976656058</v>
       </c>
       <c r="F43">
-        <v>-4.270181921532583</v>
+        <v>-4.684660521727732</v>
       </c>
       <c r="G43">
-        <v>-14.32217595793844</v>
+        <v>-18.03817228576802</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-4.577742181773039</v>
       </c>
       <c r="E44">
-        <v>-31.19025172482784</v>
+        <v>-36.12610725422822</v>
       </c>
       <c r="F44">
-        <v>-4.678563737643127</v>
+        <v>-5.013843787191422</v>
       </c>
       <c r="G44">
-        <v>-13.99336264334141</v>
+        <v>-19.36430565207096</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-4.451437331306459</v>
       </c>
       <c r="E45">
-        <v>-29.25833225757154</v>
+        <v>-34.59072361345358</v>
       </c>
       <c r="F45">
-        <v>-4.822153771611797</v>
+        <v>-4.857168033360729</v>
       </c>
       <c r="G45">
-        <v>-14.35940304252755</v>
+        <v>-18.17436978452641</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-4.312638482159154</v>
       </c>
       <c r="E46">
-        <v>-29.5879191243238</v>
+        <v>-36.01239274342161</v>
       </c>
       <c r="F46">
-        <v>-4.311103271230879</v>
+        <v>-4.804888109835247</v>
       </c>
       <c r="G46">
-        <v>-14.21531320320354</v>
+        <v>-18.80422093664599</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-4.16938227423289</v>
       </c>
       <c r="E47">
-        <v>-29.18695445026264</v>
+        <v>-35.86928390783122</v>
       </c>
       <c r="F47">
-        <v>-4.970581471212816</v>
+        <v>-4.37028349522168</v>
       </c>
       <c r="G47">
-        <v>-14.11049802088467</v>
+        <v>-18.49392019270456</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-4.030326717349396</v>
       </c>
       <c r="E48">
-        <v>-30.44104060686582</v>
+        <v>-34.74399434471719</v>
       </c>
       <c r="F48">
-        <v>-4.806574665867346</v>
+        <v>-4.805123366177642</v>
       </c>
       <c r="G48">
-        <v>-13.83132302610347</v>
+        <v>-17.13253779277223</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-3.902711362397477</v>
       </c>
       <c r="E49">
-        <v>-28.79114317962222</v>
+        <v>-35.97042058208152</v>
       </c>
       <c r="F49">
-        <v>-4.379390566448058</v>
+        <v>-5.089003218382227</v>
       </c>
       <c r="G49">
-        <v>-14.22039985642463</v>
+        <v>-17.70758286348917</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-3.795924903340512</v>
       </c>
       <c r="E50">
-        <v>-28.20732325360534</v>
+        <v>-35.66941970750268</v>
       </c>
       <c r="F50">
-        <v>-5.005424260909368</v>
+        <v>-5.013062636730583</v>
       </c>
       <c r="G50">
-        <v>-13.25368414295651</v>
+        <v>-17.23127315820822</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-3.715597922667517</v>
       </c>
       <c r="E51">
-        <v>-27.87117009954196</v>
+        <v>-35.41662217449849</v>
       </c>
       <c r="F51">
-        <v>-4.978087308249582</v>
+        <v>-5.102412829898745</v>
       </c>
       <c r="G51">
-        <v>-14.1406752987479</v>
+        <v>-17.85937468701029</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-3.667308008657865</v>
       </c>
       <c r="E52">
-        <v>-29.16428490938025</v>
+        <v>-34.55665590349388</v>
       </c>
       <c r="F52">
-        <v>-4.892954333529071</v>
+        <v>-5.251211638096218</v>
       </c>
       <c r="G52">
-        <v>-14.11025635106031</v>
+        <v>-19.04156387799296</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-3.653312863919853</v>
       </c>
       <c r="E53">
-        <v>-29.39247471462675</v>
+        <v>-34.3391714108015</v>
       </c>
       <c r="F53">
-        <v>-5.162349353328303</v>
+        <v>-5.158752582065348</v>
       </c>
       <c r="G53">
-        <v>-14.31451204501503</v>
+        <v>-18.04269614624743</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-3.673033578636935</v>
       </c>
       <c r="E54">
-        <v>-28.72571125868539</v>
+        <v>-34.20919741407035</v>
       </c>
       <c r="F54">
-        <v>-4.769853138901245</v>
+        <v>-4.88541453342879</v>
       </c>
       <c r="G54">
-        <v>-13.41044840587762</v>
+        <v>-17.45039816745258</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-3.723558531793586</v>
       </c>
       <c r="E55">
-        <v>-28.4756896802479</v>
+        <v>-36.24925457639281</v>
       </c>
       <c r="F55">
-        <v>-4.92339020864273</v>
+        <v>-5.247450021720105</v>
       </c>
       <c r="G55">
-        <v>-14.41378206355562</v>
+        <v>-19.00871333460677</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-3.799216447299623</v>
       </c>
       <c r="E56">
-        <v>-29.02545095325309</v>
+        <v>-35.02693340071644</v>
       </c>
       <c r="F56">
-        <v>-4.872672586038927</v>
+        <v>-5.195836933953877</v>
       </c>
       <c r="G56">
-        <v>-14.47730481136315</v>
+        <v>-18.2382434501611</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-3.89516241289289</v>
       </c>
       <c r="E57">
-        <v>-27.66896467815146</v>
+        <v>-34.64377242221644</v>
       </c>
       <c r="F57">
-        <v>-4.782062446051106</v>
+        <v>-5.237621442485889</v>
       </c>
       <c r="G57">
-        <v>-14.23200993963085</v>
+        <v>-17.93292673252905</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-4.003209961022351</v>
       </c>
       <c r="E58">
-        <v>-27.73777936917202</v>
+        <v>-35.36003889177265</v>
       </c>
       <c r="F58">
-        <v>-4.907233730818529</v>
+        <v>-5.693510957514389</v>
       </c>
       <c r="G58">
-        <v>-14.7758349106397</v>
+        <v>-17.7711983065718</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-4.117307333561709</v>
       </c>
       <c r="E59">
-        <v>-27.70356221957006</v>
+        <v>-34.39766797379558</v>
       </c>
       <c r="F59">
-        <v>-4.874358313703625</v>
+        <v>-5.396860165060843</v>
       </c>
       <c r="G59">
-        <v>-14.57729321828576</v>
+        <v>-17.83722382680703</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-4.230324117854413</v>
       </c>
       <c r="E60">
-        <v>-27.83647293169519</v>
+        <v>-36.94830152353486</v>
       </c>
       <c r="F60">
-        <v>-4.949290772226062</v>
+        <v>-5.096676385634359</v>
       </c>
       <c r="G60">
-        <v>-14.2462353538131</v>
+        <v>-18.94025456340018</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-4.335183230084931</v>
       </c>
       <c r="E61">
-        <v>-28.52174878937991</v>
+        <v>-35.05370347481278</v>
       </c>
       <c r="F61">
-        <v>-5.024122998292762</v>
+        <v>-5.034275469181472</v>
       </c>
       <c r="G61">
-        <v>-14.22594502020291</v>
+        <v>-17.96749544905012</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-4.42554477480956</v>
       </c>
       <c r="E62">
-        <v>-28.25386238098217</v>
+        <v>-35.83797403854218</v>
       </c>
       <c r="F62">
-        <v>-5.028130639787506</v>
+        <v>-5.609297470610985</v>
       </c>
       <c r="G62">
-        <v>-14.19307792408902</v>
+        <v>-18.42558391168292</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-4.495003863538914</v>
       </c>
       <c r="E63">
-        <v>-28.41524360919351</v>
+        <v>-35.71811438850716</v>
       </c>
       <c r="F63">
-        <v>-4.979448315892381</v>
+        <v>-5.733668552467303</v>
       </c>
       <c r="G63">
-        <v>-13.59174050069919</v>
+        <v>-17.45198391876589</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-4.539810317457694</v>
       </c>
       <c r="E64">
-        <v>-28.9122209891653</v>
+        <v>-35.32983397014149</v>
       </c>
       <c r="F64">
-        <v>-5.126206855176759</v>
+        <v>-5.462273853757712</v>
       </c>
       <c r="G64">
-        <v>-14.63294679934645</v>
+        <v>-18.77025142886752</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-4.556838379401882</v>
       </c>
       <c r="E65">
-        <v>-28.55648671349275</v>
+        <v>-36.69718858286152</v>
       </c>
       <c r="F65">
-        <v>-4.809539392801966</v>
+        <v>-5.957123144474678</v>
       </c>
       <c r="G65">
-        <v>-14.39992411992823</v>
+        <v>-18.64990647742394</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-4.546744359144153</v>
       </c>
       <c r="E66">
-        <v>-28.86880198037975</v>
+        <v>-36.07837713818738</v>
       </c>
       <c r="F66">
-        <v>-5.160004245210978</v>
+        <v>-5.75564679639838</v>
       </c>
       <c r="G66">
-        <v>-14.89804700976743</v>
+        <v>-18.05896913284572</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-4.511595077624136</v>
       </c>
       <c r="E67">
-        <v>-27.61439203788503</v>
+        <v>-35.83969033019109</v>
       </c>
       <c r="F67">
-        <v>-5.372617993017916</v>
+        <v>-5.772884293683235</v>
       </c>
       <c r="G67">
-        <v>-14.68953064370367</v>
+        <v>-18.7925595399839</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-4.454950718505835</v>
       </c>
       <c r="E68">
-        <v>-28.05489029003315</v>
+        <v>-35.60535991419018</v>
       </c>
       <c r="F68">
-        <v>-5.309199841394392</v>
+        <v>-5.616898569899074</v>
       </c>
       <c r="G68">
-        <v>-13.52244416147116</v>
+        <v>-18.57756443629978</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-4.381859190422657</v>
       </c>
       <c r="E69">
-        <v>-28.19241551717209</v>
+        <v>-36.76357148333997</v>
       </c>
       <c r="F69">
-        <v>-5.173939870028274</v>
+        <v>-5.802610257932694</v>
       </c>
       <c r="G69">
-        <v>-15.19307786240898</v>
+        <v>-17.75017965294297</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-4.297398383512998</v>
       </c>
       <c r="E70">
-        <v>-27.98860701598288</v>
+        <v>-35.9302009401824</v>
       </c>
       <c r="F70">
-        <v>-5.203753641222431</v>
+        <v>-5.505386235236412</v>
       </c>
       <c r="G70">
-        <v>-14.60780982706676</v>
+        <v>-16.96530061903763</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-4.206879675631201</v>
       </c>
       <c r="E71">
-        <v>-28.72186205577887</v>
+        <v>-35.70817891653434</v>
       </c>
       <c r="F71">
-        <v>-5.399240064609087</v>
+        <v>-6.270577783877712</v>
       </c>
       <c r="G71">
-        <v>-14.61330202211641</v>
+        <v>-18.01407648006044</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-4.115459605285528</v>
       </c>
       <c r="E72">
-        <v>-28.59491081544784</v>
+        <v>-37.02063936733339</v>
       </c>
       <c r="F72">
-        <v>-5.293075669898899</v>
+        <v>-5.01572500956318</v>
       </c>
       <c r="G72">
-        <v>-13.91414294385942</v>
+        <v>-18.41623824162556</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-4.026945002034521</v>
       </c>
       <c r="E73">
-        <v>-28.93161644334015</v>
+        <v>-35.67777700628384</v>
       </c>
       <c r="F73">
-        <v>-5.345524580374553</v>
+        <v>-5.94729125177085</v>
       </c>
       <c r="G73">
-        <v>-15.04192497417693</v>
+        <v>-16.91963164332338</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-3.943481513337934</v>
       </c>
       <c r="E74">
-        <v>-29.02542378240904</v>
+        <v>-37.04360778750029</v>
       </c>
       <c r="F74">
-        <v>-5.458107994089033</v>
+        <v>-5.5821087957163</v>
       </c>
       <c r="G74">
-        <v>-14.14781614547611</v>
+        <v>-16.87665414113257</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-3.864784637825368</v>
       </c>
       <c r="E75">
-        <v>-28.13596808866648</v>
+        <v>-36.03793333682487</v>
       </c>
       <c r="F75">
-        <v>-5.657018059951459</v>
+        <v>-5.819180919458296</v>
       </c>
       <c r="G75">
-        <v>-14.46310919209076</v>
+        <v>-17.80547072926711</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-3.788724925983247</v>
       </c>
       <c r="E76">
-        <v>-28.84253683113527</v>
+        <v>-38.40768378503877</v>
       </c>
       <c r="F76">
-        <v>-5.779407686980281</v>
+        <v>-5.410164573917206</v>
       </c>
       <c r="G76">
-        <v>-14.27727337351654</v>
+        <v>-17.20701513576921</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-3.711597783075415</v>
       </c>
       <c r="E77">
-        <v>-29.30613482919651</v>
+        <v>-36.40633149005987</v>
       </c>
       <c r="F77">
-        <v>-5.603686109824421</v>
+        <v>-6.057263651431708</v>
       </c>
       <c r="G77">
-        <v>-14.30921186160666</v>
+        <v>-18.98110669535479</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-3.627824867602273</v>
       </c>
       <c r="E78">
-        <v>-29.24789412498386</v>
+        <v>-37.59304527461394</v>
       </c>
       <c r="F78">
-        <v>-5.62716535548937</v>
+        <v>-6.230007247774503</v>
       </c>
       <c r="G78">
-        <v>-14.36360246954411</v>
+        <v>-18.26328772716569</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-3.534527380772465</v>
       </c>
       <c r="E79">
-        <v>-29.17088289600942</v>
+        <v>-36.34464914560139</v>
       </c>
       <c r="F79">
-        <v>-5.569854756726687</v>
+        <v>-5.825115343531952</v>
       </c>
       <c r="G79">
-        <v>-14.6065319564886</v>
+        <v>-17.79490015736022</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-3.427689484961401</v>
       </c>
       <c r="E80">
-        <v>-29.79024002180149</v>
+        <v>-36.66272236718915</v>
       </c>
       <c r="F80">
-        <v>-5.748971811866621</v>
+        <v>-5.980893975465412</v>
       </c>
       <c r="G80">
-        <v>-13.79618655102242</v>
+        <v>-18.43993512659566</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-3.305246011886438</v>
       </c>
       <c r="E81">
-        <v>-30.47629024854153</v>
+        <v>-37.51481815036843</v>
       </c>
       <c r="F81">
-        <v>-5.339554536502576</v>
+        <v>-6.695350919971153</v>
       </c>
       <c r="G81">
-        <v>-14.45385621730849</v>
+        <v>-18.45015147012985</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-3.166611162338666</v>
       </c>
       <c r="E82">
-        <v>-30.85654847520261</v>
+        <v>-38.63552263354968</v>
       </c>
       <c r="F82">
-        <v>-5.508669055253707</v>
+        <v>-6.234270026429309</v>
       </c>
       <c r="G82">
-        <v>-13.1573538888548</v>
+        <v>-18.57324417437103</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-3.013320081669783</v>
       </c>
       <c r="E83">
-        <v>-30.69532121510752</v>
+        <v>-38.12694556740725</v>
       </c>
       <c r="F83">
-        <v>-5.920922660604937</v>
+        <v>-6.53092578908727</v>
       </c>
       <c r="G83">
-        <v>-13.81025305901878</v>
+        <v>-17.46032814879762</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-2.849162392134241</v>
       </c>
       <c r="E84">
-        <v>-31.11440884214738</v>
+        <v>-37.78750926968831</v>
       </c>
       <c r="F84">
-        <v>-5.901649864611404</v>
+        <v>-6.201237219507873</v>
       </c>
       <c r="G84">
-        <v>-13.96571793281573</v>
+        <v>-18.03182431469647</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-2.678676802916336</v>
       </c>
       <c r="E85">
-        <v>-32.69521534145596</v>
+        <v>-38.83467812769602</v>
       </c>
       <c r="F85">
-        <v>-5.749673439056792</v>
+        <v>-6.482313876421384</v>
       </c>
       <c r="G85">
-        <v>-14.16898708419975</v>
+        <v>-17.42493014061897</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-2.510382701172146</v>
       </c>
       <c r="E86">
-        <v>-32.18136033885759</v>
+        <v>-39.69527838506171</v>
       </c>
       <c r="F86">
-        <v>-6.182509489265382</v>
+        <v>-7.15057981199592</v>
       </c>
       <c r="G86">
-        <v>-13.82801413583697</v>
+        <v>-18.62349328983886</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-2.351622680652429</v>
       </c>
       <c r="E87">
-        <v>-34.321754899768</v>
+        <v>-40.22067420366863</v>
       </c>
       <c r="F87">
-        <v>-6.072663829817153</v>
+        <v>-6.654659856410835</v>
       </c>
       <c r="G87">
-        <v>-13.70407724248328</v>
+        <v>-18.44961185120695</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-2.211383230958771</v>
       </c>
       <c r="E88">
-        <v>-34.65632082369169</v>
+        <v>-42.17579304326622</v>
       </c>
       <c r="F88">
-        <v>-6.24647643429326</v>
+        <v>-6.566992905805161</v>
       </c>
       <c r="G88">
-        <v>-14.09110153457008</v>
+        <v>-17.76076181175925</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-2.097749597134785</v>
       </c>
       <c r="E89">
-        <v>-35.48976608667039</v>
+        <v>-41.03116010342843</v>
       </c>
       <c r="F89">
-        <v>-6.523230255915263</v>
+        <v>-7.006959542617048</v>
       </c>
       <c r="G89">
-        <v>-14.57818541030859</v>
+        <v>-17.49699244064505</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-2.01807433848217</v>
       </c>
       <c r="E90">
-        <v>-36.57103208971884</v>
+        <v>-42.16449450061708</v>
       </c>
       <c r="F90">
-        <v>-6.117238279761795</v>
+        <v>-7.591158612318476</v>
       </c>
       <c r="G90">
-        <v>-14.54406858325363</v>
+        <v>-18.5819575302304</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-1.978467485580453</v>
       </c>
       <c r="E91">
-        <v>-36.86999288675722</v>
+        <v>-42.64932424906329</v>
       </c>
       <c r="F91">
-        <v>-6.459959139505735</v>
+        <v>-7.128911791657192</v>
       </c>
       <c r="G91">
-        <v>-14.78234840898822</v>
+        <v>-18.75022924944601</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-1.982615981049995</v>
       </c>
       <c r="E92">
-        <v>-37.67672468156467</v>
+        <v>-46.58946344213112</v>
       </c>
       <c r="F92">
-        <v>-6.868202204076312</v>
+        <v>-6.860234552212485</v>
       </c>
       <c r="G92">
-        <v>-14.25014676336775</v>
+        <v>-18.88541537654215</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-2.034037834985477</v>
       </c>
       <c r="E93">
-        <v>-38.87421623425699</v>
+        <v>-44.85653644395688</v>
       </c>
       <c r="F93">
-        <v>-6.971289213885099</v>
+        <v>-7.43351739627982</v>
       </c>
       <c r="G93">
-        <v>-14.05158189719503</v>
+        <v>-18.90113550203538</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-2.132286501928371</v>
       </c>
       <c r="E94">
-        <v>-41.18105712155633</v>
+        <v>-43.57934601296657</v>
       </c>
       <c r="F94">
-        <v>-7.257861260148782</v>
+        <v>-7.461565916538611</v>
       </c>
       <c r="G94">
-        <v>-14.69924543958866</v>
+        <v>-18.48087333273429</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-2.277771700592762</v>
       </c>
       <c r="E95">
-        <v>-42.48144239641393</v>
+        <v>-47.17482078507361</v>
       </c>
       <c r="F95">
-        <v>-7.161139839646808</v>
+        <v>-7.541768862661361</v>
       </c>
       <c r="G95">
-        <v>-14.75082042854497</v>
+        <v>-18.16766924035492</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-2.471911384102376</v>
       </c>
       <c r="E96">
-        <v>-43.21812322679673</v>
+        <v>-48.2417609605988</v>
       </c>
       <c r="F96">
-        <v>-7.259025116349715</v>
+        <v>-7.767949611791349</v>
       </c>
       <c r="G96">
-        <v>-14.47461664838526</v>
+        <v>-19.34963000369537</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-2.709448078466351</v>
       </c>
       <c r="E97">
-        <v>-45.11537043281329</v>
+        <v>-50.25294570476685</v>
       </c>
       <c r="F97">
-        <v>-7.714468969715509</v>
+        <v>-7.674482018447571</v>
       </c>
       <c r="G97">
-        <v>-15.30064741861651</v>
+        <v>-19.38914136470657</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-2.995179725742724</v>
       </c>
       <c r="E98">
-        <v>-46.60139823537833</v>
+        <v>-50.37200494702101</v>
       </c>
       <c r="F98">
-        <v>-7.465291084749</v>
+        <v>-7.628312547068839</v>
       </c>
       <c r="G98">
-        <v>-15.63764771233216</v>
+        <v>-19.19046062943999</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-3.315703379170831</v>
       </c>
       <c r="E99">
-        <v>-49.0880852036553</v>
+        <v>-50.09586313050728</v>
       </c>
       <c r="F99">
-        <v>-8.095671222972799</v>
+        <v>-7.996544637716797</v>
       </c>
       <c r="G99">
-        <v>-15.4237997126774</v>
+        <v>-19.17277735044197</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-3.684650667347692</v>
       </c>
       <c r="E100">
-        <v>-49.71670079455605</v>
+        <v>-53.10824479667568</v>
       </c>
       <c r="F100">
-        <v>-7.847174256011392</v>
+        <v>-9.23593386353957</v>
       </c>
       <c r="G100">
-        <v>-14.77313350547966</v>
+        <v>-20.09380753546814</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-4.070707112320031</v>
       </c>
       <c r="E101">
-        <v>-50.63975097272452</v>
+        <v>-54.2204334844855</v>
       </c>
       <c r="F101">
-        <v>-8.641513982638699</v>
+        <v>-8.745871708043381</v>
       </c>
       <c r="G101">
-        <v>-15.66661664107356</v>
+        <v>-19.75087805469166</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-4.514060785053844</v>
       </c>
       <c r="E102">
-        <v>-52.92948102098588</v>
+        <v>-55.41960736527167</v>
       </c>
       <c r="F102">
-        <v>-8.549805841658468</v>
+        <v>-8.863895424675748</v>
       </c>
       <c r="G102">
-        <v>-16.06152830790768</v>
+        <v>-20.02153832634585</v>
       </c>
     </row>
   </sheetData>
